--- a/public/datos/4.4_Cuadro_de_mando.xlsx
+++ b/public/datos/4.4_Cuadro_de_mando.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicadores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reglas_Semaforo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Criterios_Semaforo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos_Historicos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard_Gerencial" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,257 +428,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Indicador</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Proceso</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Meta (%)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T1 (%)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>T2 (%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>T3 (%)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>% Cumplimiento</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tendencia</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Documentos vigentes</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>72</v>
-      </c>
-      <c r="E2" t="n">
-        <v>78</v>
-      </c>
-      <c r="F2" t="n">
-        <v>80</v>
+          <t>4.4</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Satisfacción del cliente</t>
+          <t>Título del Caso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comercial y ventas</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D3" t="n">
-        <v>82</v>
-      </c>
-      <c r="E3" t="n">
-        <v>86</v>
-      </c>
-      <c r="F3" t="n">
-        <v>88</v>
+          <t>Cuadro de mando integral (Dashboard Ejecutivo SIG)</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cumplimiento del plan de auditorías</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>60</v>
-      </c>
-      <c r="E4" t="n">
-        <v>80</v>
-      </c>
-      <c r="F4" t="n">
-        <v>95</v>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acciones correctivas cerradas a tiempo</t>
+          <t>1. Situación Problema</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
-      </c>
-      <c r="E5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F5" t="n">
-        <v>70</v>
+          <t>Al cierre del periodo, la Gerencia General y la Junta Directiva exigen un Dashboard de Control Gerencial de alto impacto visual para evaluar el SIG.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cumplimiento del plan de capacitación</t>
+          <t>2. Misión del Aprendiz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Talento humano</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>90</v>
-      </c>
-      <c r="D6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E6" t="n">
-        <v>85</v>
-      </c>
-      <c r="F6" t="n">
-        <v>92</v>
+          <t>Diseñar el Cuadro de Mando Integral calculando % cumplimiento, tendencias dinámicas con símbolos tipográficos, 3 tarjetas KPI ejecutivas y gráfico comparativo.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Entregas a tiempo</t>
+          <t>Requerimiento 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logística y distribución</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D7" t="n">
-        <v>93</v>
-      </c>
-      <c r="E7" t="n">
-        <v>91</v>
-      </c>
-      <c r="F7" t="n">
-        <v>96</v>
+          <t>% Cumplimiento T3: Dividir =T3 / Meta con formato porcentual.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proveedores evaluados</t>
+          <t>Requerimiento 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compras</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" t="n">
-        <v>65</v>
-      </c>
-      <c r="F8" t="n">
-        <v>85</v>
+          <t>Tendencia T3 vs T2: Evaluar con SI anidado: si T3 &gt; T2 -&gt; '▲ Favorable'; si T3 &lt; T2 -&gt; '▼ Desfavorable'; si T3 = T2 -&gt; '― Estable'.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mantenimientos preventivos ejecutados</t>
+          <t>Requerimiento 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>90</v>
-      </c>
-      <c r="D9" t="n">
-        <v>88</v>
-      </c>
-      <c r="E9" t="n">
-        <v>75</v>
-      </c>
-      <c r="F9" t="n">
-        <v>70</v>
+          <t>Semáforo Gerencial: Verde (&gt;= 100%), Amarillo (90% a 99.9%), Rojo (&lt; 90%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tarjetas KPI Ejecutivas: Diseñar en cabecera: a) % Promedio Cumplimiento SIG, b) Indicadores en Crisis (Rojos), c) Metas Cumplidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Requerimiento 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gráfico Comparativo: Columnas agrupadas comparando serie Meta vs serie Resultado Real T3 con leyenda y etiquetas claras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Integra cálculos matemáticos, caracteres tipográficos de tendencia (▲, ▼, ―) y un gráfico de doble serie con estética corporativa.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -690,59 +590,636 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Rango Cumplimiento</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Condición</t>
+          <t>Color Semáforo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Significado Gerencial</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>≥ 100%</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>% Cumplimiento ≥ 100%</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Meta superada o cumplida a cabalidad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>90% a 99.9%</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Amarillo</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>90% ≤ % Cumplimiento &lt; 100%</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Desempeño cercano a la meta (en tolerancia)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>&lt; 90%</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Rojo</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Desempeño crítico (incumplimiento de meta)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meta (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>T1 (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>T2 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T3 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IND-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Documentos vigentes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IND-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Satisfacción del cliente</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comercial y ventas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IND-03</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>% Cumplimiento &lt; 90%</t>
-        </is>
+          <t>Cumplimiento del plan de auditorías</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IND-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Acciones correctivas cerradas a tiempo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IND-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cumplimiento del plan de capacitación</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="n">
+        <v>85</v>
+      </c>
+      <c r="G6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IND-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Entregas a tiempo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>93</v>
+      </c>
+      <c r="F7" t="n">
+        <v>91</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IND-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Proveedores evaluados</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Compras</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IND-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mantenimientos preventivos ejecutados</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="n">
+        <v>88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Meta (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>T1 (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>T2 (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>T3 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>% Cumplimiento T3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tendencia T3 vs T2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Semáforo Gerencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Documentos vigentes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Satisfacción del cliente</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comercial y ventas</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cumplimiento del plan de auditorías</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Acciones correctivas cerradas a tiempo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cumplimiento del plan de capacitación</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Entregas a tiempo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Proveedores evaluados</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Compras</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mantenimientos preventivos ejecutados</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="n">
+        <v>88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F9" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
